--- a/results.xlsx
+++ b/results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,11 +473,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>But</t>
+          <t>bayramali</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -500,41 +500,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-10-31 12:24:24</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Shohruz</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>{1: 'b', 2: 'b', 3: 'a', 4: 'b', 5: 'c', 6: 'b', 7: 'a', 8: 'c', 9: 'b', 10: 'b'}</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>10</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>100</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>5 (A’lo)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2025-10-31 12:24:00</t>
+          <t>2025-11-01 05:35:35</t>
         </is>
       </c>
     </row>
